--- a/output/yearly_population_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_45_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6015</v>
+        <v>4903</v>
       </c>
       <c r="C2" t="n">
-        <v>6374</v>
+        <v>6976</v>
       </c>
       <c r="D2" t="n">
-        <v>37586</v>
+        <v>14887</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3933</v>
+        <v>3529</v>
       </c>
       <c r="C3" t="n">
-        <v>4091</v>
+        <v>3643</v>
       </c>
       <c r="D3" t="n">
-        <v>17096</v>
+        <v>11037</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3045</v>
+        <v>2621</v>
       </c>
       <c r="C4" t="n">
-        <v>6345</v>
+        <v>3422</v>
       </c>
       <c r="D4" t="n">
-        <v>6280</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1987</v>
+        <v>1664</v>
       </c>
       <c r="C5" t="n">
-        <v>5544</v>
+        <v>4199</v>
       </c>
       <c r="D5" t="n">
-        <v>2275</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1141</v>
+        <v>947</v>
       </c>
       <c r="C6" t="n">
-        <v>3168</v>
+        <v>3940</v>
       </c>
       <c r="D6" t="n">
-        <v>1050</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>549</v>
+        <v>445</v>
       </c>
       <c r="C7" t="n">
-        <v>1697</v>
+        <v>2927</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="C8" t="n">
-        <v>787</v>
+        <v>1478</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>532</v>
       </c>
       <c r="D9" t="n">
         <v>305</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7182</v>
+        <v>6157</v>
       </c>
       <c r="C2" t="n">
-        <v>7802</v>
+        <v>5994</v>
       </c>
       <c r="D2" t="n">
-        <v>32381</v>
+        <v>17957</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3949</v>
+        <v>3382</v>
       </c>
       <c r="C3" t="n">
-        <v>4501</v>
+        <v>4518</v>
       </c>
       <c r="D3" t="n">
-        <v>18733</v>
+        <v>10818</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2930</v>
+        <v>2572</v>
       </c>
       <c r="C4" t="n">
-        <v>5091</v>
+        <v>3421</v>
       </c>
       <c r="D4" t="n">
-        <v>7854</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2176</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>5797</v>
+        <v>3753</v>
       </c>
       <c r="D5" t="n">
-        <v>2799</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1361</v>
+        <v>1135</v>
       </c>
       <c r="C6" t="n">
-        <v>4155</v>
+        <v>3977</v>
       </c>
       <c r="D6" t="n">
-        <v>1224</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>714</v>
+        <v>586</v>
       </c>
       <c r="C7" t="n">
-        <v>2345</v>
+        <v>3372</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="C8" t="n">
-        <v>1162</v>
+        <v>2073</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10039</v>
+        <v>7374</v>
       </c>
       <c r="C2" t="n">
-        <v>14494</v>
+        <v>8306</v>
       </c>
       <c r="D2" t="n">
-        <v>30216</v>
+        <v>24209</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4245</v>
+        <v>3658</v>
       </c>
       <c r="C3" t="n">
-        <v>5185</v>
+        <v>4543</v>
       </c>
       <c r="D3" t="n">
-        <v>19171</v>
+        <v>10982</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2842</v>
+        <v>2497</v>
       </c>
       <c r="C4" t="n">
-        <v>4730</v>
+        <v>3790</v>
       </c>
       <c r="D4" t="n">
-        <v>9106</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2205</v>
+        <v>1897</v>
       </c>
       <c r="C5" t="n">
-        <v>5329</v>
+        <v>3498</v>
       </c>
       <c r="D5" t="n">
-        <v>3441</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1533</v>
+        <v>1289</v>
       </c>
       <c r="C6" t="n">
-        <v>4739</v>
+        <v>3848</v>
       </c>
       <c r="D6" t="n">
-        <v>1407</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>869</v>
+        <v>719</v>
       </c>
       <c r="C7" t="n">
-        <v>3071</v>
+        <v>3580</v>
       </c>
       <c r="D7" t="n">
-        <v>758</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>410</v>
+        <v>334</v>
       </c>
       <c r="C8" t="n">
-        <v>1602</v>
+        <v>2581</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>763</v>
+        <v>1340</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>551</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8981</v>
+        <v>6686</v>
       </c>
       <c r="C2" t="n">
-        <v>9971</v>
+        <v>5648</v>
       </c>
       <c r="D2" t="n">
-        <v>25093</v>
+        <v>19788</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5097</v>
+        <v>4464</v>
       </c>
       <c r="C3" t="n">
-        <v>8553</v>
+        <v>6886</v>
       </c>
       <c r="D3" t="n">
-        <v>20281</v>
+        <v>12072</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>1752</v>
       </c>
       <c r="C4" t="n">
-        <v>7704</v>
+        <v>5468</v>
       </c>
       <c r="D4" t="n">
-        <v>8322</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>1191</v>
       </c>
       <c r="C5" t="n">
-        <v>4644</v>
+        <v>3771</v>
       </c>
       <c r="D5" t="n">
-        <v>2303</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>802</v>
+        <v>664</v>
       </c>
       <c r="C6" t="n">
-        <v>3009</v>
+        <v>3508</v>
       </c>
       <c r="D6" t="n">
-        <v>742</v>
+        <v>698</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1569</v>
+        <v>2529</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>747</v>
+        <v>1313</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>539</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5262</v>
+        <v>3984</v>
       </c>
       <c r="C2" t="n">
-        <v>4792</v>
+        <v>2771</v>
       </c>
       <c r="D2" t="n">
-        <v>18211</v>
+        <v>14090</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5740</v>
+        <v>4649</v>
       </c>
       <c r="C3" t="n">
-        <v>8337</v>
+        <v>5741</v>
       </c>
       <c r="D3" t="n">
-        <v>19961</v>
+        <v>12426</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2778</v>
+        <v>2412</v>
       </c>
       <c r="C4" t="n">
-        <v>8230</v>
+        <v>6165</v>
       </c>
       <c r="D4" t="n">
-        <v>9870</v>
+        <v>6921</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1572</v>
+        <v>1330</v>
       </c>
       <c r="C5" t="n">
-        <v>5959</v>
+        <v>4574</v>
       </c>
       <c r="D5" t="n">
-        <v>3028</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>953</v>
+        <v>787</v>
       </c>
       <c r="C6" t="n">
-        <v>3757</v>
+        <v>3778</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>2087</v>
+        <v>3019</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>984</v>
+        <v>1706</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>595</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5247</v>
+        <v>3822</v>
       </c>
       <c r="C2" t="n">
-        <v>9952</v>
+        <v>9986</v>
       </c>
       <c r="D2" t="n">
-        <v>16548</v>
+        <v>15496</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4653</v>
+        <v>3667</v>
       </c>
       <c r="C3" t="n">
-        <v>5876</v>
+        <v>3798</v>
       </c>
       <c r="D3" t="n">
-        <v>18381</v>
+        <v>11929</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3472</v>
+        <v>2917</v>
       </c>
       <c r="C4" t="n">
-        <v>8190</v>
+        <v>5825</v>
       </c>
       <c r="D4" t="n">
-        <v>11216</v>
+        <v>7542</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1843</v>
+        <v>1587</v>
       </c>
       <c r="C5" t="n">
-        <v>6881</v>
+        <v>5286</v>
       </c>
       <c r="D5" t="n">
-        <v>3986</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1107</v>
+        <v>929</v>
       </c>
       <c r="C6" t="n">
-        <v>4693</v>
+        <v>4100</v>
       </c>
       <c r="D6" t="n">
-        <v>1197</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>515</v>
+        <v>430</v>
       </c>
       <c r="C7" t="n">
-        <v>2826</v>
+        <v>3382</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1436</v>
+        <v>2262</v>
       </c>
       <c r="D8" t="n">
         <v>351</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>1031</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="D10" t="n">
         <v>213</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3160</v>
+        <v>2242</v>
       </c>
       <c r="C2" t="n">
-        <v>4752</v>
+        <v>4609</v>
       </c>
       <c r="D2" t="n">
-        <v>11534</v>
+        <v>10670</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4624</v>
+        <v>3604</v>
       </c>
       <c r="C3" t="n">
-        <v>7043</v>
+        <v>5805</v>
       </c>
       <c r="D3" t="n">
-        <v>17778</v>
+        <v>12042</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3831</v>
+        <v>3215</v>
       </c>
       <c r="C4" t="n">
-        <v>8072</v>
+        <v>5581</v>
       </c>
       <c r="D4" t="n">
-        <v>12070</v>
+        <v>8125</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1928</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>8202</v>
+        <v>6257</v>
       </c>
       <c r="D5" t="n">
-        <v>4240</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>915</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>5567</v>
+        <v>5182</v>
       </c>
       <c r="D6" t="n">
-        <v>1181</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2826</v>
+        <v>3761</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1048</v>
+        <v>1719</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>361</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4434</v>
+        <v>3036</v>
       </c>
       <c r="C2" t="n">
-        <v>6865</v>
+        <v>8324</v>
       </c>
       <c r="D2" t="n">
-        <v>13565</v>
+        <v>15473</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3414</v>
+        <v>2595</v>
       </c>
       <c r="C3" t="n">
-        <v>5378</v>
+        <v>4648</v>
       </c>
       <c r="D3" t="n">
-        <v>15904</v>
+        <v>11046</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3658</v>
+        <v>2953</v>
       </c>
       <c r="C4" t="n">
-        <v>7429</v>
+        <v>5628</v>
       </c>
       <c r="D4" t="n">
-        <v>12579</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2371</v>
+        <v>2031</v>
       </c>
       <c r="C5" t="n">
-        <v>8052</v>
+        <v>5875</v>
       </c>
       <c r="D5" t="n">
-        <v>5238</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1177</v>
+        <v>1022</v>
       </c>
       <c r="C6" t="n">
-        <v>6659</v>
+        <v>5648</v>
       </c>
       <c r="D6" t="n">
-        <v>1576</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="C7" t="n">
-        <v>3954</v>
+        <v>4418</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1695</v>
+        <v>2512</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3058,7 +3058,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>823</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3173,7 +3173,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2968</v>
+        <v>2016</v>
       </c>
       <c r="C2" t="n">
-        <v>4089</v>
+        <v>4061</v>
       </c>
       <c r="D2" t="n">
-        <v>9908</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3271</v>
+        <v>2399</v>
       </c>
       <c r="C3" t="n">
-        <v>5462</v>
+        <v>5561</v>
       </c>
       <c r="D3" t="n">
-        <v>14910</v>
+        <v>10976</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3274</v>
+        <v>2597</v>
       </c>
       <c r="C4" t="n">
-        <v>6609</v>
+        <v>5259</v>
       </c>
       <c r="D4" t="n">
-        <v>12732</v>
+        <v>8679</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2613</v>
+        <v>2217</v>
       </c>
       <c r="C5" t="n">
-        <v>7972</v>
+        <v>5885</v>
       </c>
       <c r="D5" t="n">
-        <v>5904</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1378</v>
+        <v>1217</v>
       </c>
       <c r="C6" t="n">
-        <v>7355</v>
+        <v>5957</v>
       </c>
       <c r="D6" t="n">
-        <v>1919</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>4859</v>
+        <v>5032</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2201</v>
+        <v>3082</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>972</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4149</v>
+        <v>3044</v>
       </c>
       <c r="C2" t="n">
-        <v>7454</v>
+        <v>8900</v>
       </c>
       <c r="D2" t="n">
-        <v>19584</v>
+        <v>13287</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2666</v>
+        <v>1900</v>
       </c>
       <c r="C3" t="n">
-        <v>4428</v>
+        <v>4377</v>
       </c>
       <c r="D3" t="n">
-        <v>13355</v>
+        <v>10505</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2844</v>
+        <v>2194</v>
       </c>
       <c r="C4" t="n">
-        <v>5998</v>
+        <v>5282</v>
       </c>
       <c r="D4" t="n">
-        <v>12658</v>
+        <v>8662</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2610</v>
+        <v>2167</v>
       </c>
       <c r="C5" t="n">
-        <v>7269</v>
+        <v>5498</v>
       </c>
       <c r="D5" t="n">
-        <v>6642</v>
+        <v>4938</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1653</v>
+        <v>1453</v>
       </c>
       <c r="C6" t="n">
-        <v>7525</v>
+        <v>5933</v>
       </c>
       <c r="D6" t="n">
-        <v>2391</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="C7" t="n">
-        <v>5762</v>
+        <v>5383</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>3133</v>
+        <v>3818</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1103</v>
+        <v>1674</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>479</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6796</v>
+        <v>5392</v>
       </c>
       <c r="C2" t="n">
-        <v>6516</v>
+        <v>14335</v>
       </c>
       <c r="D2" t="n">
-        <v>5544</v>
+        <v>7509</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3001</v>
+        <v>2154</v>
       </c>
       <c r="C2" t="n">
-        <v>4353</v>
+        <v>4984</v>
       </c>
       <c r="D2" t="n">
-        <v>14570</v>
+        <v>9779</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3548</v>
+        <v>2602</v>
       </c>
       <c r="C3" t="n">
-        <v>5478</v>
+        <v>5833</v>
       </c>
       <c r="D3" t="n">
-        <v>14768</v>
+        <v>11517</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3841</v>
+        <v>3099</v>
       </c>
       <c r="C4" t="n">
-        <v>8513</v>
+        <v>7211</v>
       </c>
       <c r="D4" t="n">
-        <v>12895</v>
+        <v>8871</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1575</v>
+        <v>1422</v>
       </c>
       <c r="C5" t="n">
-        <v>10578</v>
+        <v>8235</v>
       </c>
       <c r="D5" t="n">
-        <v>5977</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="C6" t="n">
-        <v>7047</v>
+        <v>6496</v>
       </c>
       <c r="D6" t="n">
-        <v>1869</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>3070</v>
+        <v>3741</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1080</v>
+        <v>1640</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>469</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7226</v>
+        <v>6436</v>
       </c>
       <c r="C2" t="n">
-        <v>4791</v>
+        <v>11027</v>
       </c>
       <c r="D2" t="n">
-        <v>16635</v>
+        <v>9363</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2887</v>
+        <v>2291</v>
       </c>
       <c r="C3" t="n">
-        <v>3336</v>
+        <v>7224</v>
       </c>
       <c r="D3" t="n">
-        <v>1570</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5648</v>
+        <v>4866</v>
       </c>
       <c r="C2" t="n">
-        <v>6221</v>
+        <v>9247</v>
       </c>
       <c r="D2" t="n">
-        <v>13909</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4153</v>
+        <v>3582</v>
       </c>
       <c r="C3" t="n">
-        <v>3587</v>
+        <v>8085</v>
       </c>
       <c r="D3" t="n">
-        <v>3985</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1288</v>
+        <v>1029</v>
       </c>
       <c r="C4" t="n">
-        <v>1997</v>
+        <v>4276</v>
       </c>
       <c r="D4" t="n">
-        <v>1497</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5548</v>
+        <v>4860</v>
       </c>
       <c r="C2" t="n">
-        <v>7539</v>
+        <v>4267</v>
       </c>
       <c r="D2" t="n">
-        <v>16106</v>
+        <v>13397</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4018</v>
+        <v>3494</v>
       </c>
       <c r="C3" t="n">
-        <v>4348</v>
+        <v>7550</v>
       </c>
       <c r="D3" t="n">
-        <v>5285</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2304</v>
+        <v>1929</v>
       </c>
       <c r="C4" t="n">
-        <v>2856</v>
+        <v>6266</v>
       </c>
       <c r="D4" t="n">
-        <v>1929</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>589</v>
+        <v>475</v>
       </c>
       <c r="C5" t="n">
-        <v>1185</v>
+        <v>2436</v>
       </c>
       <c r="D5" t="n">
-        <v>1195</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6109</v>
+        <v>4472</v>
       </c>
       <c r="C2" t="n">
-        <v>10079</v>
+        <v>5839</v>
       </c>
       <c r="D2" t="n">
-        <v>19175</v>
+        <v>15911</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3900</v>
+        <v>3395</v>
       </c>
       <c r="C3" t="n">
-        <v>5214</v>
+        <v>5139</v>
       </c>
       <c r="D3" t="n">
-        <v>6557</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>2289</v>
       </c>
       <c r="C4" t="n">
-        <v>3571</v>
+        <v>6813</v>
       </c>
       <c r="D4" t="n">
-        <v>2463</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1188</v>
+        <v>973</v>
       </c>
       <c r="C5" t="n">
-        <v>2042</v>
+        <v>4310</v>
       </c>
       <c r="D5" t="n">
-        <v>1292</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>748</v>
+        <v>1365</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>190</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6975</v>
+        <v>6751</v>
       </c>
       <c r="C2" t="n">
-        <v>13233</v>
+        <v>5012</v>
       </c>
       <c r="D2" t="n">
-        <v>28071</v>
+        <v>27856</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3662</v>
+        <v>2842</v>
       </c>
       <c r="C3" t="n">
-        <v>6307</v>
+        <v>4500</v>
       </c>
       <c r="D3" t="n">
-        <v>7538</v>
+        <v>6024</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2031</v>
+        <v>1741</v>
       </c>
       <c r="C4" t="n">
-        <v>3640</v>
+        <v>4831</v>
       </c>
       <c r="D4" t="n">
-        <v>2713</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1009</v>
+        <v>845</v>
       </c>
       <c r="C5" t="n">
-        <v>2083</v>
+        <v>4042</v>
       </c>
       <c r="D5" t="n">
-        <v>1188</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>359</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>938</v>
+        <v>1899</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>532</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
         <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5752</v>
+        <v>4898</v>
       </c>
       <c r="C2" t="n">
-        <v>4875</v>
+        <v>2690</v>
       </c>
       <c r="D2" t="n">
-        <v>37715</v>
+        <v>22241</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4423</v>
+        <v>3970</v>
       </c>
       <c r="C3" t="n">
-        <v>8954</v>
+        <v>4127</v>
       </c>
       <c r="D3" t="n">
-        <v>10584</v>
+        <v>9248</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>2000</v>
       </c>
       <c r="C4" t="n">
-        <v>5202</v>
+        <v>4533</v>
       </c>
       <c r="D4" t="n">
-        <v>3649</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1348</v>
+        <v>1139</v>
       </c>
       <c r="C5" t="n">
-        <v>2966</v>
+        <v>4373</v>
       </c>
       <c r="D5" t="n">
-        <v>1459</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>638</v>
+        <v>523</v>
       </c>
       <c r="C6" t="n">
-        <v>1585</v>
+        <v>3089</v>
       </c>
       <c r="D6" t="n">
-        <v>827</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>684</v>
+        <v>1295</v>
       </c>
       <c r="D7" t="n">
         <v>556</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>389</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5492</v>
+        <v>5068</v>
       </c>
       <c r="C2" t="n">
-        <v>3516</v>
+        <v>5392</v>
       </c>
       <c r="D2" t="n">
-        <v>41309</v>
+        <v>18372</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4176</v>
+        <v>3639</v>
       </c>
       <c r="C3" t="n">
-        <v>5825</v>
+        <v>2912</v>
       </c>
       <c r="D3" t="n">
-        <v>14162</v>
+        <v>10661</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2975</v>
+        <v>2526</v>
       </c>
       <c r="C4" t="n">
-        <v>7218</v>
+        <v>4212</v>
       </c>
       <c r="D4" t="n">
-        <v>4869</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1674</v>
+        <v>1379</v>
       </c>
       <c r="C5" t="n">
-        <v>4127</v>
+        <v>4368</v>
       </c>
       <c r="D5" t="n">
-        <v>1800</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>744</v>
       </c>
       <c r="C6" t="n">
-        <v>2296</v>
+        <v>3689</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1145</v>
+        <v>2226</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>492</v>
+        <v>841</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_45_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4903</v>
+        <v>6271</v>
       </c>
       <c r="C2" t="n">
-        <v>6976</v>
+        <v>13400</v>
       </c>
       <c r="D2" t="n">
-        <v>14887</v>
+        <v>32422</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3529</v>
+        <v>4199</v>
       </c>
       <c r="C3" t="n">
-        <v>3643</v>
+        <v>6042</v>
       </c>
       <c r="D3" t="n">
-        <v>11037</v>
+        <v>16574</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2621</v>
+        <v>3169</v>
       </c>
       <c r="C4" t="n">
-        <v>3422</v>
+        <v>4984</v>
       </c>
       <c r="D4" t="n">
-        <v>5054</v>
+        <v>8017</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1664</v>
+        <v>2072</v>
       </c>
       <c r="C5" t="n">
-        <v>4199</v>
+        <v>4778</v>
       </c>
       <c r="D5" t="n">
-        <v>1942</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>1104</v>
       </c>
       <c r="C6" t="n">
-        <v>3940</v>
+        <v>3564</v>
       </c>
       <c r="D6" t="n">
-        <v>976</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>515</v>
       </c>
       <c r="C7" t="n">
-        <v>2927</v>
+        <v>2011</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C8" t="n">
-        <v>1478</v>
+        <v>914</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>532</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6157</v>
+        <v>7672</v>
       </c>
       <c r="C2" t="n">
-        <v>5994</v>
+        <v>11551</v>
       </c>
       <c r="D2" t="n">
-        <v>17957</v>
+        <v>28203</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3382</v>
+        <v>4153</v>
       </c>
       <c r="C3" t="n">
-        <v>4518</v>
+        <v>8161</v>
       </c>
       <c r="D3" t="n">
-        <v>10818</v>
+        <v>17515</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2572</v>
+        <v>3078</v>
       </c>
       <c r="C4" t="n">
-        <v>3421</v>
+        <v>5320</v>
       </c>
       <c r="D4" t="n">
-        <v>5876</v>
+        <v>9010</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>2240</v>
       </c>
       <c r="C5" t="n">
-        <v>3753</v>
+        <v>4771</v>
       </c>
       <c r="D5" t="n">
-        <v>2342</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>1380</v>
       </c>
       <c r="C6" t="n">
-        <v>3977</v>
+        <v>4020</v>
       </c>
       <c r="D6" t="n">
-        <v>1111</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>586</v>
+        <v>676</v>
       </c>
       <c r="C7" t="n">
-        <v>3372</v>
+        <v>2679</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="C8" t="n">
-        <v>2073</v>
+        <v>1356</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>921</v>
+        <v>592</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7374</v>
+        <v>10682</v>
       </c>
       <c r="C2" t="n">
-        <v>8306</v>
+        <v>9174</v>
       </c>
       <c r="D2" t="n">
-        <v>24209</v>
+        <v>28408</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>4474</v>
       </c>
       <c r="C3" t="n">
-        <v>4543</v>
+        <v>8453</v>
       </c>
       <c r="D3" t="n">
-        <v>10982</v>
+        <v>17676</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2497</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>3790</v>
+        <v>6409</v>
       </c>
       <c r="D4" t="n">
-        <v>6352</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1897</v>
+        <v>2283</v>
       </c>
       <c r="C5" t="n">
-        <v>3498</v>
+        <v>4847</v>
       </c>
       <c r="D5" t="n">
-        <v>2779</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1289</v>
+        <v>1558</v>
       </c>
       <c r="C6" t="n">
-        <v>3848</v>
+        <v>4241</v>
       </c>
       <c r="D6" t="n">
-        <v>1251</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>719</v>
+        <v>845</v>
       </c>
       <c r="C7" t="n">
-        <v>3580</v>
+        <v>3203</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
       <c r="C8" t="n">
-        <v>2581</v>
+        <v>1834</v>
       </c>
       <c r="D8" t="n">
         <v>476</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="C9" t="n">
-        <v>1340</v>
+        <v>862</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>551</v>
+        <v>384</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6686</v>
+        <v>9584</v>
       </c>
       <c r="C2" t="n">
-        <v>5648</v>
+        <v>6385</v>
       </c>
       <c r="D2" t="n">
-        <v>19788</v>
+        <v>23574</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4464</v>
+        <v>5319</v>
       </c>
       <c r="C3" t="n">
-        <v>6886</v>
+        <v>11776</v>
       </c>
       <c r="D3" t="n">
-        <v>12072</v>
+        <v>19180</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1752</v>
+        <v>2109</v>
       </c>
       <c r="C4" t="n">
-        <v>5468</v>
+        <v>8098</v>
       </c>
       <c r="D4" t="n">
-        <v>6067</v>
+        <v>9408</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1191</v>
+        <v>1439</v>
       </c>
       <c r="C5" t="n">
-        <v>3771</v>
+        <v>4156</v>
       </c>
       <c r="D5" t="n">
-        <v>1972</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>664</v>
+        <v>780</v>
       </c>
       <c r="C6" t="n">
-        <v>3508</v>
+        <v>3138</v>
       </c>
       <c r="D6" t="n">
-        <v>698</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>2529</v>
+        <v>1797</v>
       </c>
       <c r="D7" t="n">
         <v>466</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>1313</v>
+        <v>844</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>539</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3984</v>
+        <v>5649</v>
       </c>
       <c r="C2" t="n">
-        <v>2771</v>
+        <v>3985</v>
       </c>
       <c r="D2" t="n">
-        <v>14090</v>
+        <v>16364</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4649</v>
+        <v>6026</v>
       </c>
       <c r="C3" t="n">
-        <v>5741</v>
+        <v>8545</v>
       </c>
       <c r="D3" t="n">
-        <v>12426</v>
+        <v>18856</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2412</v>
+        <v>2861</v>
       </c>
       <c r="C4" t="n">
-        <v>6165</v>
+        <v>9900</v>
       </c>
       <c r="D4" t="n">
-        <v>6921</v>
+        <v>10619</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1330</v>
+        <v>1601</v>
       </c>
       <c r="C5" t="n">
-        <v>4574</v>
+        <v>5780</v>
       </c>
       <c r="D5" t="n">
-        <v>2460</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>787</v>
+        <v>919</v>
       </c>
       <c r="C6" t="n">
-        <v>3778</v>
+        <v>3672</v>
       </c>
       <c r="D6" t="n">
-        <v>832</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>3019</v>
+        <v>2278</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1706</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>595</v>
+        <v>409</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>164</v>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3822</v>
+        <v>6480</v>
       </c>
       <c r="C2" t="n">
-        <v>9986</v>
+        <v>11401</v>
       </c>
       <c r="D2" t="n">
-        <v>15496</v>
+        <v>18907</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3667</v>
+        <v>4933</v>
       </c>
       <c r="C3" t="n">
-        <v>3798</v>
+        <v>5695</v>
       </c>
       <c r="D3" t="n">
-        <v>11929</v>
+        <v>17249</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2917</v>
+        <v>3589</v>
       </c>
       <c r="C4" t="n">
-        <v>5825</v>
+        <v>9138</v>
       </c>
       <c r="D4" t="n">
-        <v>7542</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1587</v>
+        <v>1863</v>
       </c>
       <c r="C5" t="n">
-        <v>5286</v>
+        <v>7518</v>
       </c>
       <c r="D5" t="n">
-        <v>3113</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>929</v>
+        <v>1103</v>
       </c>
       <c r="C6" t="n">
-        <v>4100</v>
+        <v>4548</v>
       </c>
       <c r="D6" t="n">
-        <v>1070</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="C7" t="n">
-        <v>3382</v>
+        <v>2886</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>2262</v>
+        <v>1587</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
+        <v>672</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>369</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2242</v>
+        <v>3919</v>
       </c>
       <c r="C2" t="n">
-        <v>4609</v>
+        <v>5486</v>
       </c>
       <c r="D2" t="n">
-        <v>10670</v>
+        <v>13216</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3604</v>
+        <v>5098</v>
       </c>
       <c r="C3" t="n">
-        <v>5805</v>
+        <v>7366</v>
       </c>
       <c r="D3" t="n">
-        <v>12042</v>
+        <v>17035</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3215</v>
+        <v>3940</v>
       </c>
       <c r="C4" t="n">
-        <v>5581</v>
+        <v>8767</v>
       </c>
       <c r="D4" t="n">
-        <v>8125</v>
+        <v>12373</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>1923</v>
       </c>
       <c r="C5" t="n">
-        <v>6257</v>
+        <v>8995</v>
       </c>
       <c r="D5" t="n">
-        <v>3363</v>
+        <v>4817</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>883</v>
       </c>
       <c r="C6" t="n">
-        <v>5182</v>
+        <v>5395</v>
       </c>
       <c r="D6" t="n">
-        <v>1063</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>3761</v>
+        <v>2955</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1719</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="n">
         <v>375</v>
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
         <v>285</v>
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3036</v>
+        <v>4463</v>
       </c>
       <c r="C2" t="n">
-        <v>8324</v>
+        <v>4153</v>
       </c>
       <c r="D2" t="n">
-        <v>15473</v>
+        <v>17633</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2595</v>
+        <v>3915</v>
       </c>
       <c r="C3" t="n">
-        <v>4648</v>
+        <v>5854</v>
       </c>
       <c r="D3" t="n">
-        <v>11046</v>
+        <v>15428</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2953</v>
+        <v>3866</v>
       </c>
       <c r="C4" t="n">
-        <v>5628</v>
+        <v>7952</v>
       </c>
       <c r="D4" t="n">
-        <v>8517</v>
+        <v>12712</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2031</v>
+        <v>2385</v>
       </c>
       <c r="C5" t="n">
-        <v>5875</v>
+        <v>8795</v>
       </c>
       <c r="D5" t="n">
-        <v>3992</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>1136</v>
       </c>
       <c r="C6" t="n">
-        <v>5648</v>
+        <v>6851</v>
       </c>
       <c r="D6" t="n">
-        <v>1390</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>4418</v>
+        <v>3944</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2512</v>
+        <v>1774</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>823</v>
+        <v>545</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" t="n">
         <v>135</v>
-      </c>
-      <c r="D11" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2016</v>
+        <v>3061</v>
       </c>
       <c r="C2" t="n">
-        <v>4061</v>
+        <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>12102</v>
+        <v>13326</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2399</v>
+        <v>3579</v>
       </c>
       <c r="C3" t="n">
-        <v>5561</v>
+        <v>4800</v>
       </c>
       <c r="D3" t="n">
-        <v>10976</v>
+        <v>14860</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2597</v>
+        <v>3536</v>
       </c>
       <c r="C4" t="n">
-        <v>5259</v>
+        <v>7133</v>
       </c>
       <c r="D4" t="n">
-        <v>8679</v>
+        <v>12786</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2217</v>
+        <v>2653</v>
       </c>
       <c r="C5" t="n">
-        <v>5885</v>
+        <v>8658</v>
       </c>
       <c r="D5" t="n">
-        <v>4468</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1217</v>
+        <v>1321</v>
       </c>
       <c r="C6" t="n">
-        <v>5957</v>
+        <v>7702</v>
       </c>
       <c r="D6" t="n">
-        <v>1625</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>5032</v>
+        <v>4868</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>3082</v>
+        <v>2259</v>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>972</v>
+        <v>603</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3044</v>
+        <v>4053</v>
       </c>
       <c r="C2" t="n">
-        <v>8900</v>
+        <v>10639</v>
       </c>
       <c r="D2" t="n">
-        <v>13287</v>
+        <v>14836</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1900</v>
+        <v>2869</v>
       </c>
       <c r="C3" t="n">
-        <v>4377</v>
+        <v>3811</v>
       </c>
       <c r="D3" t="n">
-        <v>10505</v>
+        <v>13760</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2194</v>
+        <v>3085</v>
       </c>
       <c r="C4" t="n">
-        <v>5282</v>
+        <v>6043</v>
       </c>
       <c r="D4" t="n">
-        <v>8662</v>
+        <v>12676</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2167</v>
+        <v>2704</v>
       </c>
       <c r="C5" t="n">
-        <v>5498</v>
+        <v>7892</v>
       </c>
       <c r="D5" t="n">
-        <v>4938</v>
+        <v>6963</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1453</v>
+        <v>1601</v>
       </c>
       <c r="C6" t="n">
-        <v>5933</v>
+        <v>7989</v>
       </c>
       <c r="D6" t="n">
-        <v>1985</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C7" t="n">
-        <v>5383</v>
+        <v>5865</v>
       </c>
       <c r="D7" t="n">
-        <v>795</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>3818</v>
+        <v>3149</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1674</v>
+        <v>1105</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>479</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5392</v>
+        <v>7087</v>
       </c>
       <c r="C2" t="n">
-        <v>14335</v>
+        <v>7102</v>
       </c>
       <c r="D2" t="n">
-        <v>7509</v>
+        <v>10485</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2154</v>
+        <v>2964</v>
       </c>
       <c r="C2" t="n">
-        <v>4984</v>
+        <v>6298</v>
       </c>
       <c r="D2" t="n">
-        <v>9779</v>
+        <v>11038</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2602</v>
+        <v>3761</v>
       </c>
       <c r="C3" t="n">
-        <v>5833</v>
+        <v>5636</v>
       </c>
       <c r="D3" t="n">
-        <v>11517</v>
+        <v>15013</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3099</v>
+        <v>4076</v>
       </c>
       <c r="C4" t="n">
-        <v>7211</v>
+        <v>8687</v>
       </c>
       <c r="D4" t="n">
-        <v>8871</v>
+        <v>12866</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1422</v>
+        <v>1504</v>
       </c>
       <c r="C5" t="n">
-        <v>8235</v>
+        <v>11344</v>
       </c>
       <c r="D5" t="n">
-        <v>4575</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>6496</v>
+        <v>7156</v>
       </c>
       <c r="D6" t="n">
-        <v>1650</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>3741</v>
+        <v>3086</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1640</v>
+        <v>1082</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6436</v>
+        <v>6831</v>
       </c>
       <c r="C2" t="n">
-        <v>11027</v>
+        <v>8377</v>
       </c>
       <c r="D2" t="n">
-        <v>9363</v>
+        <v>13399</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2291</v>
+        <v>3010</v>
       </c>
       <c r="C3" t="n">
-        <v>7224</v>
+        <v>3579</v>
       </c>
       <c r="D3" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4866</v>
+        <v>4822</v>
       </c>
       <c r="C2" t="n">
-        <v>9247</v>
+        <v>5676</v>
       </c>
       <c r="D2" t="n">
-        <v>10373</v>
+        <v>29246</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3582</v>
+        <v>4043</v>
       </c>
       <c r="C3" t="n">
-        <v>8085</v>
+        <v>5427</v>
       </c>
       <c r="D3" t="n">
-        <v>3013</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1029</v>
+        <v>1342</v>
       </c>
       <c r="C4" t="n">
-        <v>4276</v>
+        <v>2141</v>
       </c>
       <c r="D4" t="n">
-        <v>1564</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4860</v>
+        <v>5858</v>
       </c>
       <c r="C2" t="n">
-        <v>4267</v>
+        <v>10357</v>
       </c>
       <c r="D2" t="n">
-        <v>13397</v>
+        <v>29398</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3494</v>
+        <v>3646</v>
       </c>
       <c r="C3" t="n">
-        <v>7550</v>
+        <v>4867</v>
       </c>
       <c r="D3" t="n">
-        <v>3973</v>
+        <v>7805</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1929</v>
+        <v>2293</v>
       </c>
       <c r="C4" t="n">
-        <v>6266</v>
+        <v>3905</v>
       </c>
       <c r="D4" t="n">
-        <v>1794</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>475</v>
+        <v>599</v>
       </c>
       <c r="C5" t="n">
-        <v>2436</v>
+        <v>1266</v>
       </c>
       <c r="D5" t="n">
-        <v>1216</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
         <v>304</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4472</v>
+        <v>7456</v>
       </c>
       <c r="C2" t="n">
-        <v>5839</v>
+        <v>7954</v>
       </c>
       <c r="D2" t="n">
-        <v>15911</v>
+        <v>31482</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3395</v>
+        <v>3833</v>
       </c>
       <c r="C3" t="n">
-        <v>5139</v>
+        <v>6742</v>
       </c>
       <c r="D3" t="n">
-        <v>5125</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2289</v>
+        <v>2503</v>
       </c>
       <c r="C4" t="n">
-        <v>6813</v>
+        <v>4294</v>
       </c>
       <c r="D4" t="n">
-        <v>2136</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>973</v>
+        <v>1194</v>
       </c>
       <c r="C5" t="n">
-        <v>4310</v>
+        <v>2607</v>
       </c>
       <c r="D5" t="n">
-        <v>1267</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>317</v>
       </c>
       <c r="C6" t="n">
-        <v>1365</v>
+        <v>777</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6751</v>
+        <v>7636</v>
       </c>
       <c r="C2" t="n">
-        <v>5012</v>
+        <v>6868</v>
       </c>
       <c r="D2" t="n">
-        <v>27856</v>
+        <v>26544</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2842</v>
+        <v>4021</v>
       </c>
       <c r="C3" t="n">
-        <v>4500</v>
+        <v>6025</v>
       </c>
       <c r="D3" t="n">
-        <v>6024</v>
+        <v>12210</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1741</v>
+        <v>1940</v>
       </c>
       <c r="C4" t="n">
-        <v>4831</v>
+        <v>4565</v>
       </c>
       <c r="D4" t="n">
-        <v>2280</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>845</v>
+        <v>959</v>
       </c>
       <c r="C5" t="n">
-        <v>4042</v>
+        <v>2542</v>
       </c>
       <c r="D5" t="n">
-        <v>1107</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>356</v>
       </c>
       <c r="C6" t="n">
-        <v>1899</v>
+        <v>1132</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4898</v>
+        <v>5760</v>
       </c>
       <c r="C2" t="n">
-        <v>2690</v>
+        <v>5537</v>
       </c>
       <c r="D2" t="n">
-        <v>22241</v>
+        <v>31045</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3970</v>
+        <v>4821</v>
       </c>
       <c r="C3" t="n">
-        <v>4127</v>
+        <v>5604</v>
       </c>
       <c r="D3" t="n">
-        <v>9248</v>
+        <v>13719</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2000</v>
+        <v>2607</v>
       </c>
       <c r="C4" t="n">
-        <v>4533</v>
+        <v>5339</v>
       </c>
       <c r="D4" t="n">
-        <v>2965</v>
+        <v>5363</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1139</v>
+        <v>1278</v>
       </c>
       <c r="C5" t="n">
-        <v>4373</v>
+        <v>3629</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>523</v>
+        <v>608</v>
       </c>
       <c r="C6" t="n">
-        <v>3089</v>
+        <v>1916</v>
       </c>
       <c r="D6" t="n">
-        <v>817</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>1295</v>
+        <v>788</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>389</v>
+        <v>293</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>81</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5068</v>
+        <v>6038</v>
       </c>
       <c r="C2" t="n">
-        <v>5392</v>
+        <v>9114</v>
       </c>
       <c r="D2" t="n">
-        <v>18372</v>
+        <v>29627</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3639</v>
+        <v>4347</v>
       </c>
       <c r="C3" t="n">
-        <v>2912</v>
+        <v>4828</v>
       </c>
       <c r="D3" t="n">
-        <v>10661</v>
+        <v>15635</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2526</v>
+        <v>3171</v>
       </c>
       <c r="C4" t="n">
-        <v>4212</v>
+        <v>5375</v>
       </c>
       <c r="D4" t="n">
-        <v>4081</v>
+        <v>6672</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1379</v>
+        <v>1671</v>
       </c>
       <c r="C5" t="n">
-        <v>4368</v>
+        <v>4472</v>
       </c>
       <c r="D5" t="n">
-        <v>1553</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>851</v>
       </c>
       <c r="C6" t="n">
-        <v>3689</v>
+        <v>2782</v>
       </c>
       <c r="D6" t="n">
-        <v>878</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>2226</v>
+        <v>1354</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>841</v>
+        <v>540</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>148</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">

--- a/output/yearly_population_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_45_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6271</v>
+        <v>877</v>
       </c>
       <c r="C2" t="n">
-        <v>13400</v>
+        <v>3360</v>
       </c>
       <c r="D2" t="n">
-        <v>32422</v>
+        <v>14643</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4199</v>
+        <v>1656</v>
       </c>
       <c r="C3" t="n">
-        <v>6042</v>
+        <v>7617</v>
       </c>
       <c r="D3" t="n">
-        <v>16574</v>
+        <v>13904</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3169</v>
+        <v>1291</v>
       </c>
       <c r="C4" t="n">
-        <v>4984</v>
+        <v>9193</v>
       </c>
       <c r="D4" t="n">
-        <v>8017</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2072</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>4778</v>
+        <v>6106</v>
       </c>
       <c r="D5" t="n">
-        <v>2936</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1104</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>3564</v>
+        <v>2609</v>
       </c>
       <c r="D6" t="n">
-        <v>1187</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>515</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>2011</v>
+        <v>814</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>914</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7672</v>
+        <v>856</v>
       </c>
       <c r="C2" t="n">
-        <v>11551</v>
+        <v>10355</v>
       </c>
       <c r="D2" t="n">
-        <v>28203</v>
+        <v>14001</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4153</v>
+        <v>1098</v>
       </c>
       <c r="C3" t="n">
-        <v>8161</v>
+        <v>4795</v>
       </c>
       <c r="D3" t="n">
-        <v>17515</v>
+        <v>13037</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3078</v>
+        <v>1272</v>
       </c>
       <c r="C4" t="n">
-        <v>5320</v>
+        <v>8169</v>
       </c>
       <c r="D4" t="n">
-        <v>9010</v>
+        <v>7617</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2240</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>4771</v>
+        <v>7608</v>
       </c>
       <c r="D5" t="n">
-        <v>3627</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1380</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
-        <v>4020</v>
+        <v>4285</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>676</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>2679</v>
+        <v>1648</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1356</v>
+        <v>549</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10682</v>
+        <v>464</v>
       </c>
       <c r="C2" t="n">
-        <v>9174</v>
+        <v>4409</v>
       </c>
       <c r="D2" t="n">
-        <v>28408</v>
+        <v>9558</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4474</v>
+        <v>1002</v>
       </c>
       <c r="C3" t="n">
-        <v>8453</v>
+        <v>6701</v>
       </c>
       <c r="D3" t="n">
-        <v>17676</v>
+        <v>12818</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>1376</v>
       </c>
       <c r="C4" t="n">
-        <v>6409</v>
+        <v>7598</v>
       </c>
       <c r="D4" t="n">
-        <v>9960</v>
+        <v>8323</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2283</v>
+        <v>861</v>
       </c>
       <c r="C5" t="n">
-        <v>4847</v>
+        <v>8769</v>
       </c>
       <c r="D5" t="n">
-        <v>4205</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1558</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>4241</v>
+        <v>5241</v>
       </c>
       <c r="D6" t="n">
-        <v>1676</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>845</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3203</v>
+        <v>1501</v>
       </c>
       <c r="D7" t="n">
-        <v>806</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1834</v>
+        <v>483</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>862</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>384</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9584</v>
+        <v>847</v>
       </c>
       <c r="C2" t="n">
-        <v>6385</v>
+        <v>9850</v>
       </c>
       <c r="D2" t="n">
-        <v>23574</v>
+        <v>14324</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5319</v>
+        <v>658</v>
       </c>
       <c r="C3" t="n">
-        <v>11776</v>
+        <v>4928</v>
       </c>
       <c r="D3" t="n">
-        <v>19180</v>
+        <v>11466</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2109</v>
+        <v>1073</v>
       </c>
       <c r="C4" t="n">
-        <v>8098</v>
+        <v>7056</v>
       </c>
       <c r="D4" t="n">
-        <v>9408</v>
+        <v>8846</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1439</v>
+        <v>982</v>
       </c>
       <c r="C5" t="n">
-        <v>4156</v>
+        <v>8108</v>
       </c>
       <c r="D5" t="n">
-        <v>2772</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>780</v>
+        <v>486</v>
       </c>
       <c r="C6" t="n">
-        <v>3138</v>
+        <v>6884</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>1797</v>
+        <v>3091</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>844</v>
+        <v>896</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>50</v>
-      </c>
-      <c r="D15" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5649</v>
+        <v>544</v>
       </c>
       <c r="C2" t="n">
-        <v>3985</v>
+        <v>6367</v>
       </c>
       <c r="D2" t="n">
-        <v>16364</v>
+        <v>10281</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6026</v>
+        <v>633</v>
       </c>
       <c r="C3" t="n">
-        <v>8545</v>
+        <v>6337</v>
       </c>
       <c r="D3" t="n">
-        <v>18856</v>
+        <v>11189</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>870</v>
       </c>
       <c r="C4" t="n">
-        <v>9900</v>
+        <v>6172</v>
       </c>
       <c r="D4" t="n">
-        <v>10619</v>
+        <v>9039</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1601</v>
+        <v>999</v>
       </c>
       <c r="C5" t="n">
-        <v>5780</v>
+        <v>7836</v>
       </c>
       <c r="D5" t="n">
-        <v>3595</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>579</v>
       </c>
       <c r="C6" t="n">
-        <v>3672</v>
+        <v>7581</v>
       </c>
       <c r="D6" t="n">
-        <v>974</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>2278</v>
+        <v>4342</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1398</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6480</v>
+        <v>484</v>
       </c>
       <c r="C2" t="n">
-        <v>11401</v>
+        <v>7891</v>
       </c>
       <c r="D2" t="n">
-        <v>18907</v>
+        <v>15098</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4933</v>
+        <v>503</v>
       </c>
       <c r="C3" t="n">
-        <v>5695</v>
+        <v>5669</v>
       </c>
       <c r="D3" t="n">
-        <v>17249</v>
+        <v>10338</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3589</v>
+        <v>684</v>
       </c>
       <c r="C4" t="n">
-        <v>9138</v>
+        <v>6118</v>
       </c>
       <c r="D4" t="n">
-        <v>11640</v>
+        <v>9094</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1863</v>
+        <v>885</v>
       </c>
       <c r="C5" t="n">
-        <v>7518</v>
+        <v>6954</v>
       </c>
       <c r="D5" t="n">
-        <v>4564</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>673</v>
       </c>
       <c r="C6" t="n">
-        <v>4548</v>
+        <v>7618</v>
       </c>
       <c r="D6" t="n">
-        <v>1338</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>2886</v>
+        <v>5684</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1587</v>
+        <v>2507</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>755</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3919</v>
+        <v>336</v>
       </c>
       <c r="C2" t="n">
-        <v>5486</v>
+        <v>4292</v>
       </c>
       <c r="D2" t="n">
-        <v>13216</v>
+        <v>10991</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5098</v>
+        <v>682</v>
       </c>
       <c r="C3" t="n">
-        <v>7366</v>
+        <v>6700</v>
       </c>
       <c r="D3" t="n">
-        <v>17035</v>
+        <v>11535</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3940</v>
+        <v>1155</v>
       </c>
       <c r="C4" t="n">
-        <v>8767</v>
+        <v>8637</v>
       </c>
       <c r="D4" t="n">
-        <v>12373</v>
+        <v>9352</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1923</v>
+        <v>662</v>
       </c>
       <c r="C5" t="n">
-        <v>8995</v>
+        <v>10496</v>
       </c>
       <c r="D5" t="n">
-        <v>4817</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>883</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>5395</v>
+        <v>7212</v>
       </c>
       <c r="D6" t="n">
-        <v>1305</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>2955</v>
+        <v>2456</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>739</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4463</v>
+        <v>194</v>
       </c>
       <c r="C2" t="n">
-        <v>4153</v>
+        <v>4019</v>
       </c>
       <c r="D2" t="n">
-        <v>17633</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3915</v>
+        <v>459</v>
       </c>
       <c r="C3" t="n">
-        <v>5854</v>
+        <v>4980</v>
       </c>
       <c r="D3" t="n">
-        <v>15428</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3866</v>
+        <v>787</v>
       </c>
       <c r="C4" t="n">
-        <v>7952</v>
+        <v>7218</v>
       </c>
       <c r="D4" t="n">
-        <v>12712</v>
+        <v>9031</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2385</v>
+        <v>614</v>
       </c>
       <c r="C5" t="n">
-        <v>8795</v>
+        <v>8551</v>
       </c>
       <c r="D5" t="n">
-        <v>5758</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1136</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>6851</v>
+        <v>7008</v>
       </c>
       <c r="D6" t="n">
-        <v>1772</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>3944</v>
+        <v>3156</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1774</v>
+        <v>878</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3061</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>3390</v>
+        <v>16509</v>
       </c>
       <c r="D2" t="n">
-        <v>13326</v>
+        <v>10528</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3579</v>
+        <v>282</v>
       </c>
       <c r="C3" t="n">
-        <v>4800</v>
+        <v>3904</v>
       </c>
       <c r="D3" t="n">
-        <v>14860</v>
+        <v>9507</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3536</v>
+        <v>562</v>
       </c>
       <c r="C4" t="n">
-        <v>7133</v>
+        <v>5934</v>
       </c>
       <c r="D4" t="n">
-        <v>12786</v>
+        <v>9051</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2653</v>
+        <v>628</v>
       </c>
       <c r="C5" t="n">
-        <v>8658</v>
+        <v>7694</v>
       </c>
       <c r="D5" t="n">
-        <v>6427</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1321</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>7702</v>
+        <v>7689</v>
       </c>
       <c r="D6" t="n">
-        <v>2091</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>4868</v>
+        <v>5035</v>
       </c>
       <c r="D7" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2259</v>
+        <v>1913</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>523</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4053</v>
+        <v>303</v>
       </c>
       <c r="C2" t="n">
-        <v>10639</v>
+        <v>12696</v>
       </c>
       <c r="D2" t="n">
-        <v>14836</v>
+        <v>10354</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2869</v>
+        <v>224</v>
       </c>
       <c r="C3" t="n">
-        <v>3811</v>
+        <v>8477</v>
       </c>
       <c r="D3" t="n">
-        <v>13760</v>
+        <v>9006</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3085</v>
+        <v>388</v>
       </c>
       <c r="C4" t="n">
-        <v>6043</v>
+        <v>4779</v>
       </c>
       <c r="D4" t="n">
-        <v>12676</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2704</v>
+        <v>551</v>
       </c>
       <c r="C5" t="n">
-        <v>7892</v>
+        <v>6706</v>
       </c>
       <c r="D5" t="n">
-        <v>6963</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1601</v>
+        <v>431</v>
       </c>
       <c r="C6" t="n">
-        <v>7989</v>
+        <v>7615</v>
       </c>
       <c r="D6" t="n">
-        <v>2605</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>529</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>5865</v>
+        <v>6203</v>
       </c>
       <c r="D7" t="n">
-        <v>879</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>3149</v>
+        <v>3227</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1105</v>
+        <v>1076</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7087</v>
+        <v>4862</v>
       </c>
       <c r="C2" t="n">
-        <v>7102</v>
+        <v>11804</v>
       </c>
       <c r="D2" t="n">
-        <v>10485</v>
+        <v>13419</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2964</v>
+        <v>401</v>
       </c>
       <c r="C2" t="n">
-        <v>6298</v>
+        <v>13077</v>
       </c>
       <c r="D2" t="n">
-        <v>11038</v>
+        <v>14495</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3761</v>
+        <v>212</v>
       </c>
       <c r="C3" t="n">
-        <v>5636</v>
+        <v>9046</v>
       </c>
       <c r="D3" t="n">
-        <v>15013</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4076</v>
+        <v>282</v>
       </c>
       <c r="C4" t="n">
-        <v>8687</v>
+        <v>6277</v>
       </c>
       <c r="D4" t="n">
-        <v>12866</v>
+        <v>8518</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1504</v>
+        <v>449</v>
       </c>
       <c r="C5" t="n">
-        <v>11344</v>
+        <v>5706</v>
       </c>
       <c r="D5" t="n">
-        <v>6315</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>488</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>7156</v>
+        <v>7181</v>
       </c>
       <c r="D6" t="n">
-        <v>2008</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>3086</v>
+        <v>6693</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>1082</v>
+        <v>4363</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>320</v>
+        <v>1844</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>580</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6831</v>
+        <v>5282</v>
       </c>
       <c r="C2" t="n">
-        <v>8377</v>
+        <v>17566</v>
       </c>
       <c r="D2" t="n">
-        <v>13399</v>
+        <v>24310</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3010</v>
+        <v>1568</v>
       </c>
       <c r="C3" t="n">
-        <v>3579</v>
+        <v>4661</v>
       </c>
       <c r="D3" t="n">
-        <v>2400</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4822</v>
+        <v>2663</v>
       </c>
       <c r="C2" t="n">
-        <v>5676</v>
+        <v>6762</v>
       </c>
       <c r="D2" t="n">
-        <v>29246</v>
+        <v>23699</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4043</v>
+        <v>2896</v>
       </c>
       <c r="C3" t="n">
-        <v>5427</v>
+        <v>10604</v>
       </c>
       <c r="D3" t="n">
-        <v>4071</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1342</v>
+        <v>750</v>
       </c>
       <c r="C4" t="n">
-        <v>2141</v>
+        <v>2912</v>
       </c>
       <c r="D4" t="n">
-        <v>1665</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5858</v>
+        <v>2190</v>
       </c>
       <c r="C2" t="n">
-        <v>10357</v>
+        <v>3975</v>
       </c>
       <c r="D2" t="n">
-        <v>29398</v>
+        <v>22789</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3646</v>
+        <v>2295</v>
       </c>
       <c r="C3" t="n">
-        <v>4867</v>
+        <v>7269</v>
       </c>
       <c r="D3" t="n">
-        <v>7805</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2293</v>
+        <v>1584</v>
       </c>
       <c r="C4" t="n">
-        <v>3905</v>
+        <v>7355</v>
       </c>
       <c r="D4" t="n">
-        <v>2076</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>599</v>
+        <v>361</v>
       </c>
       <c r="C5" t="n">
-        <v>1266</v>
+        <v>1735</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7456</v>
+        <v>2175</v>
       </c>
       <c r="C2" t="n">
-        <v>7954</v>
+        <v>5494</v>
       </c>
       <c r="D2" t="n">
-        <v>31482</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3833</v>
+        <v>1857</v>
       </c>
       <c r="C3" t="n">
-        <v>6742</v>
+        <v>4775</v>
       </c>
       <c r="D3" t="n">
-        <v>10537</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2503</v>
+        <v>1653</v>
       </c>
       <c r="C4" t="n">
-        <v>4294</v>
+        <v>7154</v>
       </c>
       <c r="D4" t="n">
-        <v>3057</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1194</v>
+        <v>817</v>
       </c>
       <c r="C5" t="n">
-        <v>2607</v>
+        <v>4720</v>
       </c>
       <c r="D5" t="n">
-        <v>1330</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="C6" t="n">
-        <v>777</v>
+        <v>1023</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>303</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7636</v>
+        <v>1741</v>
       </c>
       <c r="C2" t="n">
-        <v>6868</v>
+        <v>10318</v>
       </c>
       <c r="D2" t="n">
-        <v>26544</v>
+        <v>29476</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4021</v>
+        <v>1653</v>
       </c>
       <c r="C3" t="n">
-        <v>6025</v>
+        <v>4482</v>
       </c>
       <c r="D3" t="n">
-        <v>12210</v>
+        <v>11023</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1940</v>
+        <v>1500</v>
       </c>
       <c r="C4" t="n">
-        <v>4565</v>
+        <v>5703</v>
       </c>
       <c r="D4" t="n">
-        <v>3778</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>959</v>
+        <v>1057</v>
       </c>
       <c r="C5" t="n">
-        <v>2542</v>
+        <v>5860</v>
       </c>
       <c r="D5" t="n">
-        <v>1275</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>430</v>
       </c>
       <c r="C6" t="n">
-        <v>1132</v>
+        <v>2822</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>644</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5760</v>
+        <v>1634</v>
       </c>
       <c r="C2" t="n">
-        <v>5537</v>
+        <v>11278</v>
       </c>
       <c r="D2" t="n">
-        <v>31045</v>
+        <v>24748</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4821</v>
+        <v>1401</v>
       </c>
       <c r="C3" t="n">
-        <v>5604</v>
+        <v>6318</v>
       </c>
       <c r="D3" t="n">
-        <v>13719</v>
+        <v>12791</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2607</v>
+        <v>1345</v>
       </c>
       <c r="C4" t="n">
-        <v>5339</v>
+        <v>4986</v>
       </c>
       <c r="D4" t="n">
-        <v>5363</v>
+        <v>5452</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>1119</v>
       </c>
       <c r="C5" t="n">
-        <v>3629</v>
+        <v>5664</v>
       </c>
       <c r="D5" t="n">
-        <v>1704</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="C6" t="n">
-        <v>1916</v>
+        <v>4137</v>
       </c>
       <c r="D6" t="n">
-        <v>858</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>788</v>
+        <v>1625</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>445</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6038</v>
+        <v>1557</v>
       </c>
       <c r="C2" t="n">
-        <v>9114</v>
+        <v>7217</v>
       </c>
       <c r="D2" t="n">
-        <v>29627</v>
+        <v>19770</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4347</v>
+        <v>2088</v>
       </c>
       <c r="C3" t="n">
-        <v>4828</v>
+        <v>9640</v>
       </c>
       <c r="D3" t="n">
-        <v>15635</v>
+        <v>13877</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3171</v>
+        <v>1033</v>
       </c>
       <c r="C4" t="n">
-        <v>5375</v>
+        <v>8452</v>
       </c>
       <c r="D4" t="n">
-        <v>6672</v>
+        <v>5076</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>579</v>
       </c>
       <c r="C5" t="n">
-        <v>4472</v>
+        <v>4054</v>
       </c>
       <c r="D5" t="n">
-        <v>2319</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>215</v>
       </c>
       <c r="C6" t="n">
-        <v>2782</v>
+        <v>1592</v>
       </c>
       <c r="D6" t="n">
-        <v>983</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1354</v>
+        <v>436</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>540</v>
+        <v>273</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
